--- a/docs/xlsx/jobs-2026-09-06.xlsx
+++ b/docs/xlsx/jobs-2026-09-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="21">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,52 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>China Labor Watch</t>
+  </si>
+  <si>
+    <t>Millburn, New Jersey</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c4729e83a8c9440d8b98608ad46b8019-executive-assistant-china-labor-watch-millburn</t>
+  </si>
+  <si>
+    <t>Teaching Abroad Opportunity - Abaarso School (Somaliland)</t>
+  </si>
+  <si>
+    <t>Abaarso School of Science and Technology</t>
+  </si>
+  <si>
+    <t>Hargeisa, Somaliland, Woqoyi Galbed, SO</t>
+  </si>
+  <si>
+    <t>USD 325.00 - 325.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/147a21b54dc845cfa5c7af3799df7138-teaching-abroad-opportunity-abaarso-school-somaliland-abaarso-school-of-science-and-technology-hargeisa-somaliland</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +93,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +119,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +558,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +597,58 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-06.xlsx
+++ b/docs/xlsx/jobs-2026-09-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="65">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,84 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Community Coach I (Full-Time) [Mon-Fri (8AM-5PM)] [Lawrence L. Frank Center]</t>
+  </si>
+  <si>
+    <t>AbilityFirst</t>
+  </si>
+  <si>
+    <t>Pasadena, California</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/748986554f6f40d4a4d03b75333d4519-community-coach-i-full-time-mon-fri-8am-5pm-lawrence-l-frank-center-abilityfirst-pasadena</t>
+  </si>
+  <si>
+    <t>Community Coach I (Part-Time) [Mon-Fri (11AM-6PM)] [LLFrank]</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/7dc51e40ae5143b7919def36a0888fab-community-coach-i-part-time-mon-fri-11am-6pm-llfrank-abilityfirst-pasadena</t>
+  </si>
+  <si>
+    <t>Community Coach I (Part-Time) [Mon-Fri (1PM-6PM)] [LLFrank]</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/80170f5eeec24edb9fb63dc02b30b3d9-community-coach-i-part-time-mon-fri-1pm-6pm-llfrank-abilityfirst-pasadena</t>
+  </si>
+  <si>
+    <t>Community Field Representative – Energy Outreach (Scranton / Wilkes-Barre)</t>
+  </si>
+  <si>
+    <t>Rosales Communications</t>
+  </si>
+  <si>
+    <t>Scranton, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 20.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/07206a3c5f38401788ab876bbd9473a1-community-field-representative-energy-outreach-scranton-wilkes-barre-rosales-communications-scranton</t>
+  </si>
+  <si>
+    <t>Community Outreach Representative (Energy Efficiency – Lehigh Valley)</t>
+  </si>
+  <si>
+    <t>Allentown, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/b3fb6619ea3740f4bc6348a876f7f83a-community-outreach-representative-energy-efficiency-lehigh-valley-rosales-communications-allentown</t>
+  </si>
+  <si>
+    <t>Community Outreach Representative (Energy Efficiency Outreach — Harrisburg, PA)</t>
+  </si>
+  <si>
+    <t>Harrisburg, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Environment, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/3e102df3ab3948b08183b82582e0ef9b-community-outreach-representative-energy-efficiency-outreach-harrisburg-pa-rosales-communications-harrisburg</t>
+  </si>
+  <si>
     <t>Executive Assistant</t>
   </si>
   <si>
@@ -49,9 +127,6 @@
     <t>Millburn, New Jersey</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 60000.00 - 80000.00/year</t>
   </si>
   <si>
@@ -59,6 +134,63 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/c4729e83a8c9440d8b98608ad46b8019-executive-assistant-china-labor-watch-millburn</t>
+  </si>
+  <si>
+    <t>JOIN A PROGRESSIVE CAMPAIGN IN CALIFORNIA’S 48TH CONGRESSIONAL DISTRICT!</t>
+  </si>
+  <si>
+    <t>Worker Power</t>
+  </si>
+  <si>
+    <t>Temecula, California</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 23.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d4ad30a8cd804aedaa0a2cdcab074914-join-a-progressive-campaign-in-californias-48th-congressional-district-worker-power-temecula</t>
+  </si>
+  <si>
+    <t>Research &amp; Data Analyst, Age-Friendly Standards (Full-Time or Part-Time)</t>
+  </si>
+  <si>
+    <t>American Association for Elder Care</t>
+  </si>
+  <si>
+    <t>Las Vegas, Nevada</t>
+  </si>
+  <si>
+    <t>USD 12.00 - 12.00/hour</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2df8b3d973604fb98a4b54ab722bdf2c-research-data-analyst-age-friendly-standards-full-time-or-part-time-american-association-for-elder-care-las-vegas</t>
+  </si>
+  <si>
+    <t>Social Work Administrator</t>
+  </si>
+  <si>
+    <t>South-East Asia Center</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/beaa96a7bad24da18ee423b2a323f717-social-work-administrator-south-east-asia-center-chicago</t>
   </si>
   <si>
     <t>Teaching Abroad Opportunity - Abaarso School (Somaliland)</t>
@@ -558,7 +690,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -625,22 +757,229 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="B5" t="s">
         <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -648,6 +987,15 @@
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
